--- a/outputs/monitor_xlsx/20260331.xlsx
+++ b/outputs/monitor_xlsx/20260331.xlsx
@@ -544,10 +544,6 @@
           <t>-1.80%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-1.42%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>-0.74%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>+4.93%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.20%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>+6.24%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>-17.51%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>-0.44%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-807.46億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-166.09億</t>
@@ -807,7 +769,6 @@
           <t>32.04億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>22.6億</t>
@@ -818,8 +779,6 @@
           <t>113.0億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>106.59%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>125.97%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-985.59億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>10450口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>8159口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>103.0億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-3.35億</t>
@@ -1016,10 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1176,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1772,7 +1714,7 @@
         <v>573</v>
       </c>
       <c r="K11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
         <v>-89</v>
@@ -2217,6 +2159,112 @@
       <c r="W18" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>7150</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-6.84</v>
+      </c>
+      <c r="E19" t="n">
+        <v>301</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="G19" t="n">
+        <v>184</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-89</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-201</v>
+      </c>
+      <c r="J19" t="n">
+        <v>14</v>
+      </c>
+      <c r="K19" t="n">
+        <v>287</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1447</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-8996</v>
+      </c>
+      <c r="N19" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1465</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-9.85</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5248</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>-191</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-617</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-84</v>
+      </c>
+      <c r="I20" t="n">
+        <v>432</v>
+      </c>
+      <c r="J20" t="n">
+        <v>261</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2194</v>
+      </c>
+      <c r="L20" t="n">
+        <v>13372</v>
+      </c>
+      <c r="M20" t="n">
+        <v>-106228</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-1.92</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260331.xlsx
+++ b/outputs/monitor_xlsx/20260331.xlsx
@@ -43,10 +43,10 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="00FF0000"/>
+      <color rgb="00008000"/>
     </font>
     <font>
-      <color rgb="00008000"/>
+      <color rgb="00FF0000"/>
     </font>
   </fonts>
   <fills count="4">
@@ -94,8 +94,8 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -536,14 +536,18 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32518.16</t>
+          <t>31722.99</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-1.80%</t>
-        </is>
-      </c>
+          <t>-2.45%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -558,14 +562,18 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>320.4</t>
+          <t>307.73</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-1.42%</t>
-        </is>
-      </c>
+          <t>-3.95%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -583,6 +591,11 @@
           <t>N/A</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -605,6 +618,10 @@
           <t>-0.74%</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -619,14 +636,18 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4749.1$</t>
+          <t>4647.6$</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+4.93%</t>
-        </is>
-      </c>
+          <t>+2.69%</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -649,6 +670,10 @@
           <t>+0.20%</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -671,6 +696,10 @@
           <t>+6.24%</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -693,6 +722,10 @@
           <t>-17.51%</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -707,14 +740,18 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>102.43$</t>
+          <t>101.38$</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-0.44%</t>
-        </is>
-      </c>
+          <t>-1.46%</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -732,24 +769,25 @@
           <t>-807.46億</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-166.09億</t>
+          <t>-309.32億</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-830.44億</t>
+          <t>-1546.6億</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-424.24億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-8484.79億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -769,16 +807,19 @@
           <t>32.04億</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.6億</t>
+          <t>38.91億</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>113.0億</t>
-        </is>
-      </c>
+          <t>194.55億</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -793,14 +834,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>106.59%</t>
-        </is>
-      </c>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>125.97%</t>
-        </is>
-      </c>
+          <t>None%</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -818,6 +863,11 @@
           <t>-985.59億</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -835,11 +885,15 @@
           <t>10450口</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8159口</t>
-        </is>
-      </c>
+          <t>None口</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -857,24 +911,25 @@
           <t>103.0億</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-3.35億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-16.77億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-5.94億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-118.77億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -921,7 +976,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-166.09億</t>
+          <t>-309.32億</t>
         </is>
       </c>
     </row>
@@ -933,7 +988,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-830.44億</t>
+          <t>-1546.6億</t>
         </is>
       </c>
     </row>
@@ -945,7 +1000,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-424.24億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -957,9 +1012,13 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-8484.79億</t>
-        </is>
-      </c>
+          <t>None億</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -969,7 +1028,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22.6億</t>
+          <t>38.91億</t>
         </is>
       </c>
     </row>
@@ -981,7 +1040,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>113.0億</t>
+          <t>194.55億</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1059,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>-3.35億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1071,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>-16.77億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1083,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-5.94億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1095,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-118.77億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1114,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>125.97%</t>
+          <t>None%</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1126,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>8159口</t>
+          <t>None口</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1100,14 +1159,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1117,7 +1175,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1196,40 +1253,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1260,39 +1312,16 @@
       <c r="F4" t="n">
         <v>257738</v>
       </c>
-      <c r="G4" s="7" t="n">
-        <v>-104127</v>
-      </c>
       <c r="H4" t="n">
-        <v>-186208</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-1400</v>
+        <v>-74153</v>
       </c>
       <c r="J4" t="n">
-        <v>130</v>
-      </c>
-      <c r="K4" t="n">
-        <v>91187</v>
-      </c>
-      <c r="L4" t="n">
-        <v>15286</v>
+        <v>330</v>
       </c>
       <c r="M4" t="n">
-        <v>67196</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-4599463</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-3.61</v>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+        <v>53414</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1323,39 +1352,16 @@
       <c r="F5" t="n">
         <v>5352</v>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>1386</v>
-      </c>
       <c r="H5" t="n">
-        <v>-708</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-659</v>
+        <v>88</v>
       </c>
       <c r="J5" t="n">
-        <v>-855</v>
-      </c>
-      <c r="K5" t="n">
-        <v>188</v>
-      </c>
-      <c r="L5" t="n">
-        <v>2664</v>
+        <v>-424</v>
       </c>
       <c r="M5" t="n">
-        <v>13939</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-78910</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-10.57</v>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+        <v>11049</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1386,39 +1392,16 @@
       <c r="F6" t="n">
         <v>21389</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>-5627</v>
-      </c>
       <c r="H6" t="n">
-        <v>3886</v>
-      </c>
-      <c r="I6" t="n">
-        <v>262</v>
+        <v>6939</v>
       </c>
       <c r="J6" t="n">
-        <v>1217</v>
-      </c>
-      <c r="K6" t="n">
-        <v>662</v>
-      </c>
-      <c r="L6" t="n">
-        <v>5408</v>
+        <v>583</v>
       </c>
       <c r="M6" t="n">
-        <v>28546</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-649360</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-7.69</v>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+        <v>23178</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1449,39 +1432,16 @@
       <c r="F7" t="n">
         <v>75832</v>
       </c>
-      <c r="G7" s="7" t="n">
-        <v>-20438</v>
-      </c>
       <c r="H7" t="n">
-        <v>-36486</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1421</v>
+        <v>-9410</v>
       </c>
       <c r="J7" t="n">
-        <v>2443</v>
-      </c>
-      <c r="K7" t="n">
-        <v>663</v>
-      </c>
-      <c r="L7" t="n">
-        <v>26608</v>
+        <v>358</v>
       </c>
       <c r="M7" t="n">
-        <v>132423</v>
-      </c>
-      <c r="N7" t="n">
-        <v>-6483131</v>
-      </c>
-      <c r="O7" t="n">
-        <v>-3.24</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+        <v>106056</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1490,12 +1450,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1504,47 +1464,24 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>90.2</v>
+        <v>1510</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-3.01</v>
+        <v>-7.65</v>
       </c>
       <c r="F8" t="n">
-        <v>248002</v>
-      </c>
-      <c r="G8" s="6" t="n">
-        <v>5078</v>
+        <v>6030</v>
       </c>
       <c r="H8" t="n">
-        <v>-57022</v>
-      </c>
-      <c r="I8" t="n">
-        <v>29414</v>
+        <v>125</v>
       </c>
       <c r="J8" t="n">
-        <v>-32518</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7520</v>
-      </c>
-      <c r="L8" t="n">
-        <v>113232</v>
+        <v>543</v>
       </c>
       <c r="M8" t="n">
-        <v>630482</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-1122189</v>
-      </c>
-      <c r="O8" t="n">
-        <v>-5.87</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>9533</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1553,12 +1490,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1567,47 +1504,24 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2600</v>
+        <v>1465</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>-6.64</v>
+        <v>-9.85</v>
       </c>
       <c r="F9" t="n">
-        <v>5256</v>
-      </c>
-      <c r="G9" s="7" t="n">
-        <v>-105</v>
+        <v>5248</v>
       </c>
       <c r="H9" t="n">
-        <v>-374</v>
-      </c>
-      <c r="I9" t="n">
-        <v>52</v>
+        <v>-381</v>
       </c>
       <c r="J9" t="n">
-        <v>416</v>
-      </c>
-      <c r="K9" t="n">
-        <v>153</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1822</v>
+        <v>998</v>
       </c>
       <c r="M9" t="n">
-        <v>9628</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-89562</v>
-      </c>
-      <c r="O9" t="n">
-        <v>-8.26</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>11178</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1616,12 +1530,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>光聖</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1630,47 +1544,24 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1900</v>
+        <v>2600</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>-9.949999999999999</v>
+        <v>-6.64</v>
       </c>
       <c r="F10" t="n">
-        <v>2987</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>-423</v>
+        <v>5256</v>
       </c>
       <c r="H10" t="n">
-        <v>-852</v>
-      </c>
-      <c r="I10" t="n">
-        <v>61</v>
+        <v>-581</v>
       </c>
       <c r="J10" t="n">
-        <v>954</v>
-      </c>
-      <c r="K10" t="n">
-        <v>122</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3913</v>
+        <v>160</v>
       </c>
       <c r="M10" t="n">
-        <v>20404</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-19439</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-8.35</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+        <v>7576</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1679,61 +1570,38 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>光聖</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1575</v>
+        <v>1900</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>-7.89</v>
+        <v>-9.949999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>4659</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>-447</v>
+        <v>2987</v>
       </c>
       <c r="H11" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I11" t="n">
-        <v>294</v>
+        <v>461</v>
       </c>
       <c r="J11" t="n">
-        <v>573</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-89</v>
+        <v>-60</v>
       </c>
       <c r="M11" t="n">
-        <v>180</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>16230</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1742,58 +1610,38 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>341.5</v>
+        <v>7150</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>-9.890000000000001</v>
+        <v>-6.84</v>
       </c>
       <c r="F12" t="n">
-        <v>1993</v>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>4</v>
+        <v>301</v>
       </c>
       <c r="H12" t="n">
-        <v>2561</v>
+        <v>123</v>
       </c>
       <c r="J12" t="n">
-        <v>1932</v>
-      </c>
-      <c r="K12" t="n">
-        <v>-103</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-520</v>
+        <v>-75</v>
       </c>
       <c r="M12" t="n">
-        <v>-1494</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>1160</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1802,61 +1650,38 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1510</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>-7.65</v>
+        <v>2315</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>6030</v>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>-662</v>
+        <v>2730</v>
       </c>
       <c r="H13" t="n">
-        <v>-293</v>
-      </c>
-      <c r="I13" t="n">
-        <v>286</v>
+        <v>-21</v>
       </c>
       <c r="J13" t="n">
-        <v>1443</v>
-      </c>
-      <c r="K13" t="n">
-        <v>413</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2057</v>
+        <v>578</v>
       </c>
       <c r="M13" t="n">
-        <v>11765</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-140232</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-7.76</v>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+        <v>265</v>
+      </c>
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1865,12 +1690,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1879,44 +1704,24 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>788</v>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>-9.94</v>
+        <v>449.5</v>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>952</v>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>-199</v>
+        <v>3871</v>
       </c>
       <c r="H14" t="n">
-        <v>14</v>
+        <v>1759</v>
       </c>
       <c r="J14" t="n">
-        <v>-4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>-19</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-60</v>
+        <v>1692</v>
       </c>
       <c r="M14" t="n">
-        <v>-386</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+        <v>-1408</v>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1939,44 +1744,24 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>810</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>-10</v>
+        <v>974</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>1422</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>-32</v>
+        <v>1350</v>
       </c>
       <c r="H15" t="n">
-        <v>-621</v>
+        <v>1137</v>
       </c>
       <c r="J15" t="n">
-        <v>3517</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-59</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-125</v>
+        <v>2078</v>
       </c>
       <c r="M15" t="n">
-        <v>-557</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+        <v>-793</v>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1985,286 +1770,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3030</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>德律</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>255.5</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>-4.49</v>
+        <v>1600</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>7180</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>104</v>
+        <v>904</v>
       </c>
       <c r="H16" t="n">
-        <v>-348</v>
+        <v>37</v>
       </c>
       <c r="J16" t="n">
-        <v>-8</v>
-      </c>
-      <c r="K16" t="n">
-        <v>271</v>
-      </c>
-      <c r="L16" t="n">
-        <v>7093</v>
+        <v>-10</v>
       </c>
       <c r="M16" t="n">
-        <v>32332</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-59030</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+        <v>157</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>華夏</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>17.35</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>-5.71</v>
-      </c>
-      <c r="F17" t="n">
-        <v>75079</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>-3735</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-4294</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>139</v>
-      </c>
-      <c r="L17" t="n">
-        <v>8838</v>
-      </c>
-      <c r="M17" t="n">
-        <v>39482</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-145167</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>台達化</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>23.05</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>-5.34</v>
-      </c>
-      <c r="F18" t="n">
-        <v>82061</v>
-      </c>
-      <c r="G18" s="6" t="n">
-        <v>3361</v>
-      </c>
-      <c r="H18" t="n">
-        <v>5322</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>251</v>
-      </c>
-      <c r="L18" t="n">
-        <v>8702</v>
-      </c>
-      <c r="M18" t="n">
-        <v>40773</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-98798</v>
-      </c>
-      <c r="O18" t="n">
-        <v>9.76</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>7150</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>-6.84</v>
-      </c>
-      <c r="E19" t="n">
-        <v>301</v>
-      </c>
-      <c r="F19" s="6" t="n">
-        <v>51</v>
-      </c>
-      <c r="G19" t="n">
-        <v>184</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-89</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-201</v>
-      </c>
-      <c r="J19" t="n">
-        <v>14</v>
-      </c>
-      <c r="K19" t="n">
-        <v>287</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1447</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-8996</v>
-      </c>
-      <c r="N19" t="n">
-        <v>6.66</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>1465</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>-9.85</v>
-      </c>
-      <c r="E20" t="n">
-        <v>5248</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>-191</v>
-      </c>
-      <c r="G20" t="n">
-        <v>-617</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-84</v>
-      </c>
-      <c r="I20" t="n">
-        <v>432</v>
-      </c>
-      <c r="J20" t="n">
-        <v>261</v>
-      </c>
-      <c r="K20" t="n">
-        <v>2194</v>
-      </c>
-      <c r="L20" t="n">
-        <v>13372</v>
-      </c>
-      <c r="M20" t="n">
-        <v>-106228</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-1.92</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260331.xlsx
+++ b/outputs/monitor_xlsx/20260331.xlsx
@@ -544,10 +544,6 @@
           <t>-2.45%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-3.95%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -591,11 +583,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -618,10 +605,6 @@
           <t>-0.74%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -644,10 +627,6 @@
           <t>+2.69%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -670,10 +649,6 @@
           <t>+0.20%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -696,10 +671,6 @@
           <t>+6.24%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -722,10 +693,6 @@
           <t>-17.51%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -748,10 +715,6 @@
           <t>-1.46%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -769,7 +732,6 @@
           <t>-807.46億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-309.32億</t>
@@ -807,7 +769,6 @@
           <t>32.04億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>38.91億</t>
@@ -818,8 +779,6 @@
           <t>194.55億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -837,15 +796,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>None%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -863,11 +818,6 @@
           <t>-985.59億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -885,15 +835,11 @@
           <t>10450口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>None口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -911,7 +857,6 @@
           <t>103.0億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>None億</t>
@@ -1016,10 +961,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1141,7 +1083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1175,6 +1117,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1805,6 +1748,39 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>368.5</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-9.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>11917</v>
+      </c>
+      <c r="G17" t="n">
+        <v>161</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>31280</v>
+      </c>
+      <c r="N17" t="n">
+        <v>10.9</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260331.xlsx
+++ b/outputs/monitor_xlsx/20260331.xlsx
@@ -961,7 +961,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1238,7 +1237,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1246,23 +1245,41 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>72.34999999999999</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>-2.1</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>257738</v>
       </c>
+      <c r="G4" s="7" t="n">
+        <v>-104127</v>
+      </c>
       <c r="H4" t="n">
-        <v>-74153</v>
+        <v>-268441</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-1400</v>
       </c>
       <c r="J4" t="n">
-        <v>330</v>
+        <v>-1270</v>
+      </c>
+      <c r="K4" t="n">
+        <v>91187</v>
+      </c>
+      <c r="L4" t="n">
+        <v>15286</v>
       </c>
       <c r="M4" t="n">
-        <v>53414</v>
+        <v>68700</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-4599463</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-4.38</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1286,23 +1303,41 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>787</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>-5.64</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="6" t="n">
         <v>5352</v>
       </c>
+      <c r="G5" s="6" t="n">
+        <v>1386</v>
+      </c>
       <c r="H5" t="n">
-        <v>88</v>
+        <v>896</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-659</v>
       </c>
       <c r="J5" t="n">
-        <v>-424</v>
+        <v>-1516</v>
+      </c>
+      <c r="K5" t="n">
+        <v>188</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2664</v>
       </c>
       <c r="M5" t="n">
-        <v>11049</v>
+        <v>13713</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-78910</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-12.64</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1326,23 +1361,41 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>1380</v>
       </c>
       <c r="E6" s="6" t="n">
         <v>-7.07</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="7" t="n">
         <v>21389</v>
       </c>
+      <c r="G6" s="7" t="n">
+        <v>-5627</v>
+      </c>
       <c r="H6" t="n">
-        <v>6939</v>
+        <v>-3857</v>
+      </c>
+      <c r="I6" t="n">
+        <v>262</v>
       </c>
       <c r="J6" t="n">
-        <v>583</v>
+        <v>1215</v>
+      </c>
+      <c r="K6" t="n">
+        <v>662</v>
+      </c>
+      <c r="L6" t="n">
+        <v>5408</v>
       </c>
       <c r="M6" t="n">
-        <v>23178</v>
+        <v>28586</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-649360</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-1.55</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1366,23 +1419,41 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1760</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>-1.12</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>75832</v>
       </c>
+      <c r="G7" s="7" t="n">
+        <v>-20438</v>
+      </c>
       <c r="H7" t="n">
-        <v>-9410</v>
+        <v>-51745</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1421</v>
       </c>
       <c r="J7" t="n">
-        <v>358</v>
+        <v>3173</v>
+      </c>
+      <c r="K7" t="n">
+        <v>663</v>
+      </c>
+      <c r="L7" t="n">
+        <v>26608</v>
       </c>
       <c r="M7" t="n">
-        <v>106056</v>
+        <v>132664</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-6483131</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-4.81</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1406,23 +1477,41 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>1510</v>
       </c>
       <c r="E8" s="6" t="n">
         <v>-7.65</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>6030</v>
       </c>
+      <c r="G8" s="7" t="n">
+        <v>-662</v>
+      </c>
       <c r="H8" t="n">
-        <v>125</v>
+        <v>-963</v>
+      </c>
+      <c r="I8" t="n">
+        <v>286</v>
       </c>
       <c r="J8" t="n">
-        <v>543</v>
+        <v>1522</v>
+      </c>
+      <c r="K8" t="n">
+        <v>413</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2057</v>
       </c>
       <c r="M8" t="n">
-        <v>9533</v>
+        <v>11590</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-140232</v>
+      </c>
+      <c r="O8" t="n">
+        <v>-0.4</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1446,23 +1535,41 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1465</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>-9.85</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>5248</v>
       </c>
+      <c r="G9" s="7" t="n">
+        <v>-191</v>
+      </c>
       <c r="H9" t="n">
-        <v>-381</v>
+        <v>-617</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-84</v>
       </c>
       <c r="J9" t="n">
-        <v>998</v>
+        <v>432</v>
+      </c>
+      <c r="K9" t="n">
+        <v>261</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2194</v>
       </c>
       <c r="M9" t="n">
-        <v>11178</v>
+        <v>13372</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-106228</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-1.92</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1486,23 +1593,41 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2600</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>-6.64</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>5256</v>
       </c>
+      <c r="G10" s="7" t="n">
+        <v>-105</v>
+      </c>
       <c r="H10" t="n">
-        <v>-581</v>
+        <v>15</v>
+      </c>
+      <c r="I10" t="n">
+        <v>52</v>
       </c>
       <c r="J10" t="n">
-        <v>160</v>
+        <v>391</v>
+      </c>
+      <c r="K10" t="n">
+        <v>153</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1822</v>
       </c>
       <c r="M10" t="n">
-        <v>7576</v>
+        <v>9398</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-89562</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.9</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1526,23 +1651,41 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>1900</v>
       </c>
       <c r="E11" s="6" t="n">
         <v>-9.949999999999999</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="7" t="n">
         <v>2987</v>
       </c>
+      <c r="G11" s="7" t="n">
+        <v>-423</v>
+      </c>
       <c r="H11" t="n">
-        <v>461</v>
+        <v>-996</v>
+      </c>
+      <c r="I11" t="n">
+        <v>61</v>
       </c>
       <c r="J11" t="n">
-        <v>-60</v>
+        <v>432</v>
+      </c>
+      <c r="K11" t="n">
+        <v>122</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3913</v>
       </c>
       <c r="M11" t="n">
-        <v>16230</v>
+        <v>20143</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-19439</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.14</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1566,23 +1709,41 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>7150</v>
       </c>
       <c r="E12" s="6" t="n">
         <v>-6.84</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>301</v>
       </c>
+      <c r="G12" s="6" t="n">
+        <v>51</v>
+      </c>
       <c r="H12" t="n">
-        <v>123</v>
+        <v>184</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-89</v>
       </c>
       <c r="J12" t="n">
-        <v>-75</v>
+        <v>-201</v>
+      </c>
+      <c r="K12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L12" t="n">
+        <v>287</v>
       </c>
       <c r="M12" t="n">
-        <v>1160</v>
+        <v>1447</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-8996</v>
+      </c>
+      <c r="O12" t="n">
+        <v>6.66</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1606,23 +1767,41 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2182</v>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>-447</v>
       </c>
       <c r="H13" t="n">
-        <v>-21</v>
+        <v>-468</v>
+      </c>
+      <c r="I13" t="n">
+        <v>294</v>
       </c>
       <c r="J13" t="n">
-        <v>578</v>
+        <v>872</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-89</v>
       </c>
       <c r="M13" t="n">
-        <v>265</v>
+        <v>176</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1646,23 +1825,41 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>1759</v>
+        <v>1763</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>1692</v>
       </c>
+      <c r="K14" t="n">
+        <v>-103</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-520</v>
+      </c>
       <c r="M14" t="n">
-        <v>-1408</v>
+        <v>-1928</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1686,23 +1883,41 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>6341</v>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>-32</v>
       </c>
       <c r="H15" t="n">
-        <v>1137</v>
+        <v>1105</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
       </c>
       <c r="J15" t="n">
         <v>2078</v>
       </c>
+      <c r="K15" t="n">
+        <v>-59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-125</v>
+      </c>
       <c r="M15" t="n">
-        <v>-793</v>
+        <v>-918</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1726,23 +1941,41 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>1168</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>180</v>
       </c>
       <c r="H16" t="n">
-        <v>37</v>
+        <v>217</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>-10</v>
       </c>
+      <c r="K16" t="n">
+        <v>-23</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-107</v>
+      </c>
       <c r="M16" t="n">
-        <v>157</v>
+        <v>50</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1761,26 +1994,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>368.5</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>-9.9</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="7" t="n">
         <v>11917</v>
       </c>
-      <c r="G17" t="n">
-        <v>161</v>
+      <c r="G17" s="7" t="n">
+        <v>-700</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-401</v>
       </c>
       <c r="I17" t="n">
-        <v>-3</v>
+        <v>333</v>
+      </c>
+      <c r="J17" t="n">
+        <v>329</v>
+      </c>
+      <c r="K17" t="n">
+        <v>242</v>
       </c>
       <c r="L17" t="n">
-        <v>31280</v>
+        <v>7769</v>
+      </c>
+      <c r="M17" t="n">
+        <v>39049</v>
       </c>
       <c r="N17" t="n">
-        <v>10.9</v>
+        <v>-22064</v>
+      </c>
+      <c r="O17" t="n">
+        <v>9.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260331.xlsx
+++ b/outputs/monitor_xlsx/20260331.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1789,7 +1789,7 @@
         <v>872</v>
       </c>
       <c r="K13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>-89</v>
@@ -2034,6 +2034,165 @@
       </c>
       <c r="O17" t="n">
         <v>9.800000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1490</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="F18" t="n">
+        <v>11429</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>313</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-3410</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-856</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-2051</v>
+      </c>
+      <c r="K18" t="n">
+        <v>231</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6105</v>
+      </c>
+      <c r="M18" t="n">
+        <v>31078</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400973</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-11.02</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>444.5</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-9.93</v>
+      </c>
+      <c r="F19" t="n">
+        <v>10008</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>-381</v>
+      </c>
+      <c r="H19" t="n">
+        <v>292</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-147</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-1141</v>
+      </c>
+      <c r="K19" t="n">
+        <v>896</v>
+      </c>
+      <c r="L19" t="n">
+        <v>30455</v>
+      </c>
+      <c r="M19" t="n">
+        <v>155292</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393861</v>
+      </c>
+      <c r="O19" t="n">
+        <v>-9.130000000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>522</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F20" t="n">
+        <v>22840</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>-2707</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3654</v>
+      </c>
+      <c r="I20" t="n">
+        <v>163</v>
+      </c>
+      <c r="J20" t="n">
+        <v>5213</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1359</v>
+      </c>
+      <c r="L20" t="n">
+        <v>8518</v>
+      </c>
+      <c r="M20" t="n">
+        <v>44498</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161092</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.74</v>
       </c>
     </row>
   </sheetData>
